--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-servicerequest-common.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$51</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -333,13 +336,190 @@
 </t>
   </si>
   <si>
-    <t>ServiceRequest.implicitRules</t>
+    <t>ServiceRequest.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>エレメント相互参照のためのユニークID</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ServiceRequest.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>実装によって定義される追加コンテンツ</t>
+  </si>
+  <si>
+    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>拡張子は常にURLで切り片にされます。</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>ServiceRequest.meta.versionId</t>
+  </si>
+  <si>
+    <t>バージョン固有の識別子</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>ServiceRequest.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>「リソースのバージョンが最後に変更されたとき」</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4/http.html#read)のインタラクションで同じ値を持つべきです。</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>ServiceRequest.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>「リソースがどこから来たかを特定する」</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
+  </si>
+  <si>
+    <t>「プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。」</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>ServiceRequest.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>このリソースが適合を主張するプロファイル</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url) への参照です。</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>ServiceRequest.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>このリソースに適用されたセキュリティラベル</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>ServiceRequest.meta.tag</t>
+  </si>
+  <si>
+    <t>このリソースに適用されたタグ</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>「様々なタグを表すコードで、一般的にはワークフローに関連しています。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>ServiceRequest.implicitRules</t>
+  </si>
+  <si>
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
@@ -435,28 +615,10 @@
     <t>ServiceRequest.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>実装によって定義される追加コンテンツ</t>
-  </si>
-  <si>
     <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
   </si>
   <si>
-    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.modifierExtension</t>
@@ -710,9 +872,6 @@
     <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
   </si>
   <si>
@@ -1325,10 +1484,6 @@
   </si>
   <si>
     <t>ServiceRequest.patientInstruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>患者、消費者向けの説明</t>
@@ -1488,6 +1643,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1663,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO43"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.71484375" customWidth="true" bestFit="true"/>
@@ -1694,7 +1864,7 @@
     <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1833,7 +2003,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1948,7 +2118,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>90</v>
       </c>
@@ -2065,7 +2235,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -2180,7 +2350,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2202,10 +2372,10 @@
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>105</v>
@@ -2216,9 +2386,7 @@
       <c r="M5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>82</v>
@@ -2267,7 +2435,7 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2279,7 +2447,7 @@
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2288,7 +2456,7 @@
         <v>82</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>82</v>
@@ -2297,7 +2465,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2306,14 +2474,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2325,16 +2493,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2360,43 +2528,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2405,7 +2573,7 @@
         <v>82</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>82</v>
@@ -2414,16 +2582,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2439,10 +2607,10 @@
         <v>82</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>122</v>
@@ -2522,53 +2690,53 @@
         <v>82</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" hidden="true">
+      <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>127</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2618,19 +2786,19 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2639,7 +2807,7 @@
         <v>82</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>82</v>
@@ -2648,23 +2816,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>82</v>
@@ -2673,19 +2841,19 @@
         <v>82</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2735,19 +2903,19 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2756,7 +2924,7 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>82</v>
@@ -2765,16 +2933,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2787,26 +2955,24 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -2854,7 +3020,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2866,7 +3032,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -2875,7 +3041,7 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>82</v>
@@ -2884,12 +3050,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2912,16 +3078,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2947,13 +3113,13 @@
         <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>82</v>
@@ -2971,7 +3137,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2986,27 +3152,27 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>158</v>
-      </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3029,16 +3195,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3064,13 +3230,13 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
@@ -3088,7 +3254,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3103,13 +3269,13 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>82</v>
@@ -3118,12 +3284,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3134,28 +3300,28 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3166,7 +3332,7 @@
         <v>82</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>82</v>
@@ -3205,13 +3371,13 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
@@ -3220,13 +3386,13 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3235,23 +3401,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3260,18 +3426,20 @@
         <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3296,13 +3464,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3320,13 +3488,13 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
@@ -3335,13 +3503,13 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -3350,23 +3518,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3375,18 +3543,20 @@
         <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3435,13 +3605,13 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
@@ -3450,13 +3620,13 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -3465,23 +3635,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3490,23 +3660,21 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3554,28 +3722,28 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
@@ -3584,44 +3752,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>113</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>200</v>
+        <v>115</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3647,13 +3815,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3671,53 +3839,53 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3726,21 +3894,23 @@
         <v>92</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -3764,13 +3934,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -3788,42 +3958,42 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3846,20 +4016,18 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -3883,11 +4051,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -3905,7 +4075,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3920,27 +4090,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3951,7 +4121,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -3963,22 +4133,22 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q20" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
         <v>82</v>
       </c>
@@ -3998,13 +4168,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4022,13 +4192,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4037,27 +4207,27 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4068,43 +4238,39 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>239</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q21" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>82</v>
@@ -4143,13 +4309,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4158,13 +4324,13 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>82</v>
@@ -4173,23 +4339,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4201,17 +4367,15 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4236,11 +4400,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4258,13 +4424,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4273,31 +4439,31 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4316,17 +4482,15 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4351,11 +4515,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4373,7 +4539,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4382,37 +4548,37 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4431,19 +4597,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>267</v>
+        <v>200</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4492,7 +4658,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4507,13 +4673,13 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -4522,12 +4688,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4544,21 +4710,23 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>274</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4583,13 +4751,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4607,7 +4775,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -4622,35 +4790,35 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -4659,21 +4827,23 @@
         <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4698,13 +4868,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4722,10 +4892,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>91</v>
@@ -4737,38 +4907,38 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>288</v>
+        <v>190</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -4780,16 +4950,20 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4813,13 +4987,11 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -4837,13 +5009,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -4852,27 +5024,27 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4895,20 +5067,22 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>303</v>
+        <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="R28" t="s" s="2">
         <v>82</v>
       </c>
@@ -4928,13 +5102,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -4952,7 +5126,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4967,31 +5141,31 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5004,26 +5178,32 @@
         <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q29" s="2"/>
+      <c r="Q29" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="R29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5067,7 +5247,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5082,31 +5262,31 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5125,16 +5305,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5160,13 +5340,11 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5184,7 +5362,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5199,38 +5377,38 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>330</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5242,16 +5420,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5277,13 +5455,11 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5301,53 +5477,53 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5359,18 +5535,20 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>344</v>
+        <v>317</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5418,13 +5596,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5433,27 +5611,27 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5461,10 +5639,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5476,13 +5654,13 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>219</v>
+        <v>324</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5509,13 +5687,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5533,13 +5711,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -5548,38 +5726,38 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5591,13 +5769,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5648,13 +5826,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -5663,38 +5841,38 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -5706,17 +5884,15 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>219</v>
+        <v>344</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5741,13 +5917,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -5765,13 +5941,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -5780,27 +5956,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5811,7 +5987,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -5823,17 +5999,15 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -5858,13 +6032,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -5882,13 +6056,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -5897,38 +6071,38 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -5937,16 +6111,16 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5997,13 +6171,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6012,38 +6186,38 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6052,19 +6226,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6114,13 +6288,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6129,38 +6303,38 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6172,16 +6346,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>397</v>
+        <v>270</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6207,13 +6381,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6231,13 +6405,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6246,31 +6420,31 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6289,20 +6463,18 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>219</v>
+        <v>394</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6326,13 +6498,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6350,7 +6522,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6365,27 +6537,27 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6405,16 +6577,16 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>414</v>
+        <v>270</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6441,13 +6613,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6465,7 +6637,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6480,27 +6652,27 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6511,7 +6683,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6523,13 +6695,13 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6580,13 +6752,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6598,24 +6770,24 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6635,19 +6807,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>426</v>
+        <v>270</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6673,13 +6845,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -6697,7 +6869,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6712,22 +6884,972 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="B45" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K45" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO43" t="s" s="2">
+      <c r="L45" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO51">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI50">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>